--- a/notebooks/prediction/planning_optimal.xlsx
+++ b/notebooks/prediction/planning_optimal.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8621577748660575</v>
+        <v>0.852108206411805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8094827984318589</v>
+        <v>0.7972164876533278</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8197885330277261</v>
+        <v>0.7738314252911194</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,14 +549,14 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8701946590885972</v>
+        <v>0.8091037273406982</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
     </row>
@@ -576,11 +576,11 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8848386533332595</v>
+        <v>0.8407438909164584</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8292895615702929</v>
+        <v>0.8328103393015236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8435742638327859</v>
+        <v>0.8015508796229507</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -642,17 +642,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8213443948764995</v>
+        <v>0.8540205811009263</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.80633375861428</v>
+        <v>0.7589804475957697</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.828256322879984</v>
+        <v>0.7942859741172407</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -717,14 +717,14 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8356434889514038</v>
+        <v>0.8495817762432677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.832516742475105</v>
+        <v>0.8019812323830344</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8601737672632391</v>
+        <v>0.8666870088288279</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7691072117198597</v>
+        <v>0.7551669604850538</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8372207121415572</v>
+        <v>0.8135311434967351</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8478065452190362</v>
+        <v>0.8349172033444801</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8371771465648304</v>
+        <v>0.8189202799941554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8298188869399254</v>
+        <v>0.887059009436405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7762549356980757</v>
+        <v>0.7523383588501902</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8588235402348067</v>
+        <v>0.846679003551753</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8413802906548308</v>
+        <v>0.839584069850641</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8228840659363101</v>
+        <v>0.8186863191200026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8155331587550617</v>
+        <v>0.8110294197544908</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1029,14 +1029,14 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8220378774585145</v>
+        <v>0.8116500811143355</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.811083120701117</v>
+        <v>0.8101272961450002</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8578269994276084</v>
+        <v>0.8645512049676365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8337260713480941</v>
+        <v>0.8396809582758432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8088443857250793</v>
+        <v>0.8133227536172579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8641072475548947</v>
+        <v>0.8654987234057803</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8917361269093524</v>
+        <v>0.8673520459757224</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8246705507991291</v>
+        <v>0.8402986306304713</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.837451311072918</v>
+        <v>0.8173232126717617</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8291741091795644</v>
+        <v>0.8451810750094328</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1272,11 +1272,11 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8451168609387947</v>
+        <v>0.8584535338661887</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8340630696449446</v>
+        <v>0.8171824459389692</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8199786727046554</v>
+        <v>0.8368827357436672</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1341,14 +1341,14 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8384653245559848</v>
+        <v>0.8218195101227425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -1365,14 +1365,14 @@
         <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8465655644734702</v>
+        <v>0.864636657213924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8280782494882141</v>
+        <v>0.7906254240960787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8064420570714822</v>
+        <v>0.8232739804283022</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1440,11 +1440,11 @@
         <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8498188221093381</v>
+        <v>0.8669753026480628</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8312879186688048</v>
+        <v>0.8148899343278674</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8068997859954835</v>
+        <v>0.7857816989975748</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1512,11 +1512,11 @@
         <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8343988837617816</v>
+        <v>0.8557542165120443</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1536,11 @@
         <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8493433432145553</v>
+        <v>0.8663223391831524</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8513155730083737</v>
+        <v>0.8665477507042163</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8144869563555477</v>
+        <v>0.796480756817442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8025903629534173</v>
+        <v>0.7795518696910204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7912624171285918</v>
+        <v>0.8101477189497515</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8515421115990842</v>
+        <v>0.8665700392289597</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8572462592462098</v>
+        <v>0.8715952526439321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8126015181493278</v>
+        <v>0.7931739416989414</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7654636917692244</v>
+        <v>0.7789368220049926</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7913833386970289</v>
+        <v>0.8082917820323597</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8677992772574378</v>
+        <v>0.882202957615708</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8125462332501213</v>
+        <v>0.8247498172358174</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8299218933991712</v>
+        <v>0.8093823230627812</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8205174195646037</v>
+        <v>0.8335814090690229</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8307726166465066</v>
+        <v>0.8472717241807417</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8141309375542756</v>
+        <v>0.8258543317280119</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8566224007379442</v>
+        <v>0.8672249781620969</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8353092285117718</v>
+        <v>0.8119169678350893</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8087544971042211</v>
+        <v>0.819196484305642</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8666096456123121</v>
+        <v>0.8809790683515144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2010,13 +2010,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
         <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8908875975945985</v>
+        <v>0.8686416448452773</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8194385049663067</v>
+        <v>0.8293917271998023</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8322053581777246</v>
+        <v>0.8079907918217207</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8236112739100602</v>
+        <v>0.8336241558344678</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2112,11 +2112,11 @@
         <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>0.841501691124656</v>
+        <v>0.8537331494418058</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8282907098574729</v>
+        <v>0.8382345019996942</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8143984394156056</v>
+        <v>0.8243418290329531</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8308430296002014</v>
+        <v>0.8444956360441267</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2208,11 +2208,11 @@
         <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8396025859948362</v>
+        <v>0.8500994094694505</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>0.839998159745727</v>
+        <v>0.8332813689202974</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8373540978755099</v>
+        <v>0.8091632060674363</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2280,11 +2280,11 @@
         <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8427040986340457</v>
+        <v>0.8506037972190165</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8228710805526888</v>
+        <v>0.797238689480406</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7995635620271317</v>
+        <v>0.7697774063457143</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8253695242332689</v>
+        <v>0.8366337833982526</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2373,14 +2373,14 @@
         <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8406410891600331</v>
+        <v>0.8476531914990358</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
         <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8426680227722786</v>
+        <v>0.847220119803843</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
         <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8434705445260713</v>
+        <v>0.8140928673021721</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
         <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8316066867173321</v>
+        <v>0.7983604079545147</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7815634626330752</v>
+        <v>0.788651162927801</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8429471507216946</v>
+        <v>0.8465358079081835</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8476995699333424</v>
+        <v>0.8499331666965678</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>0.8400086634086841</v>
+        <v>0.8451743559403853</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8304688232113617</v>
+        <v>0.7945501635773013</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7809551267912893</v>
+        <v>0.7843512043808446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>7</v>
       </c>
       <c r="E91" t="n">
-        <v>0.857708863537721</v>
+        <v>0.859142202319521</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>0.8682979443372587</v>
+        <v>0.868416868074976</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8183677340998794</v>
+        <v>0.8213189442952475</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8097394427867852</v>
+        <v>0.8095112593487057</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>0.8191432374896425</v>
+        <v>0.8204227505308209</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8378607507735965</v>
+        <v>0.8367274505923494</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8791554335391883</v>
+        <v>0.8754056631916702</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8229127171063665</v>
+        <v>0.821658705220078</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7983477669532855</v>
+        <v>0.7940570272580543</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>0.853905981237238</v>
+        <v>0.8513175429719867</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>0.879078730188235</v>
+        <v>0.8743996475682114</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8441717800123868</v>
+        <v>0.8424273266592757</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8209950201439136</v>
+        <v>0.8193788648855808</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8141736430351181</v>
+        <v>0.8107812115640353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8287846753091523</v>
+        <v>0.8238225777943929</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>7</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8197976999296599</v>
+        <v>0.8179926803445748</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8729399678339003</v>
+        <v>0.8732122845119902</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8222662367001929</v>
+        <v>0.8237920505831942</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8316719893253213</v>
+        <v>0.8309699549819485</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3072,11 +3072,11 @@
         <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8488716055648495</v>
+        <v>0.8664334651195642</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
         <v>7</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8951306150417137</v>
+        <v>0.8947229289045239</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8364842756830082</v>
+        <v>0.8357741736402416</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>6</v>
       </c>
       <c r="E113" t="n">
-        <v>0.815662798255381</v>
+        <v>0.8172123311746</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>6</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8300931261043356</v>
+        <v>0.8286461324402781</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8172712976282294</v>
+        <v>0.8166557442058217</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>6</v>
       </c>
       <c r="E116" t="n">
-        <v>0.8354143181232492</v>
+        <v>0.8337776781332614</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>7</v>
       </c>
       <c r="E117" t="n">
-        <v>0.8385497271412552</v>
+        <v>0.8367036689411511</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>6</v>
       </c>
       <c r="E118" t="n">
-        <v>0.8378883853103175</v>
+        <v>0.8378640666152491</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3288,11 +3288,11 @@
         <v>6</v>
       </c>
       <c r="E119" t="n">
-        <v>0.8266997891243059</v>
+        <v>0.8615851233703922</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7757197004376036</v>
+        <v>0.7735914100300182</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>6</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8389524594701903</v>
+        <v>0.8362254759277962</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>7</v>
       </c>
       <c r="E122" t="n">
-        <v>0.8453502077044863</v>
+        <v>0.8434613064081984</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>6</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8367068550803445</v>
+        <v>0.8359803575457949</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3408,11 +3408,11 @@
         <v>6</v>
       </c>
       <c r="E124" t="n">
-        <v>0.8283111543366404</v>
+        <v>0.8628019925319788</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
         <v>5</v>
       </c>
       <c r="E125" t="n">
-        <v>0.7771887345747515</v>
+        <v>0.7740365591916171</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>7</v>
       </c>
       <c r="E126" t="n">
-        <v>0.8563380385890152</v>
+        <v>0.8538167741563586</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>7</v>
       </c>
       <c r="E127" t="n">
-        <v>0.8687751702588015</v>
+        <v>0.867037501342025</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>6</v>
       </c>
       <c r="E128" t="n">
-        <v>0.8172838519317935</v>
+        <v>0.8172695155095573</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="E129" t="n">
-        <v>0.8096839683224457</v>
+        <v>0.8071559968620841</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3549,14 +3549,14 @@
         <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8176147648782441</v>
+        <v>0.8150162407846162</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>7</v>
       </c>
       <c r="E131" t="n">
-        <v>0.837338956403526</v>
+        <v>0.834685004978813</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8807843622535168</v>
+        <v>0.8773116631941363</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>6</v>
       </c>
       <c r="E133" t="n">
-        <v>0.8240704488272619</v>
+        <v>0.8224030528405701</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>6</v>
       </c>
       <c r="E134" t="n">
-        <v>0.7996548787511961</v>
+        <v>0.7954278497984916</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>6</v>
       </c>
       <c r="E135" t="n">
-        <v>0.8544829252994421</v>
+        <v>0.8506751927462491</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="E136" t="n">
-        <v>0.8809372343198218</v>
+        <v>0.8766470099940445</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>7</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8133017208325055</v>
+        <v>0.8122016753985253</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="E138" t="n">
-        <v>0.8238902019731926</v>
+        <v>0.8228857998896127</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>6</v>
       </c>
       <c r="E139" t="n">
-        <v>0.8165666069647279</v>
+        <v>0.8137980615249789</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>6</v>
       </c>
       <c r="E140" t="n">
-        <v>0.83113719477798</v>
+        <v>0.8267224196231726</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>7</v>
       </c>
       <c r="E141" t="n">
-        <v>0.8220121079537088</v>
+        <v>0.820900895034768</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>7</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8102746099276633</v>
+        <v>0.8115005183529544</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>6</v>
       </c>
       <c r="E143" t="n">
-        <v>0.8259567660514755</v>
+        <v>0.828479644024011</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>6</v>
       </c>
       <c r="E144" t="n">
-        <v>0.8347876385004834</v>
+        <v>0.8351191125734889</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>6</v>
       </c>
       <c r="E145" t="n">
-        <v>0.8523853330901175</v>
+        <v>0.8521078861120975</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>7</v>
       </c>
       <c r="E146" t="n">
-        <v>0.8667282315043661</v>
+        <v>0.8675228720275527</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>7</v>
       </c>
       <c r="E147" t="n">
-        <v>0.8404396158276183</v>
+        <v>0.8412003878391151</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>6</v>
       </c>
       <c r="E148" t="n">
-        <v>0.8201476395732226</v>
+        <v>0.8232233885562781</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="E149" t="n">
-        <v>0.7966294192304516</v>
+        <v>0.7967077048137935</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>6</v>
       </c>
       <c r="E150" t="n">
-        <v>0.8218648072445032</v>
+        <v>0.8227436542510986</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>6</v>
       </c>
       <c r="E151" t="n">
-        <v>0.8396008544498021</v>
+        <v>0.8395882471643314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>7</v>
       </c>
       <c r="E152" t="n">
-        <v>0.8434752984480426</v>
+        <v>0.8435350475889265</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>6</v>
       </c>
       <c r="E153" t="n">
-        <v>0.8427757494377367</v>
+        <v>0.8448091420260343</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>6</v>
       </c>
       <c r="E154" t="n">
-        <v>0.8319672406321825</v>
+        <v>0.8311920936661538</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>5</v>
       </c>
       <c r="E155" t="n">
-        <v>0.7809401714440548</v>
+        <v>0.7807806477402196</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>0.8440146157235811</v>
+        <v>0.8433193823303839</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>7</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8515337500909363</v>
+        <v>0.8518881870038583</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>6</v>
       </c>
       <c r="E158" t="n">
-        <v>0.8426119775483103</v>
+        <v>0.8444541728857792</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>6</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7969051515213168</v>
+        <v>0.7962221424989027</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>5</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7829344995094069</v>
+        <v>0.7822195761131518</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>7</v>
       </c>
       <c r="E161" t="n">
-        <v>0.8616224683896461</v>
+        <v>0.861553481130889</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>7</v>
       </c>
       <c r="E162" t="n">
-        <v>0.8417620734562951</v>
+        <v>0.8425849375098644</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>6</v>
       </c>
       <c r="E163" t="n">
-        <v>0.8241678777367178</v>
+        <v>0.8269526187819665</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="E164" t="n">
-        <v>0.8158493162405612</v>
+        <v>0.8159108354587749</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>6</v>
       </c>
       <c r="E165" t="n">
-        <v>0.8248344262441</v>
+        <v>0.8251315897161311</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>7</v>
       </c>
       <c r="E166" t="n">
-        <v>0.8110728459956843</v>
+        <v>0.810978589807926</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>7</v>
       </c>
       <c r="E167" t="n">
-        <v>0.8553585896072279</v>
+        <v>0.8540828197033375</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="E168" t="n">
-        <v>0.832830376095242</v>
+        <v>0.8337709349815292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>6</v>
       </c>
       <c r="E169" t="n">
-        <v>0.8075315302068538</v>
+        <v>0.8055491519696786</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>6</v>
       </c>
       <c r="E170" t="n">
-        <v>0.863175139282689</v>
+        <v>0.8623981114589807</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>7</v>
       </c>
       <c r="E171" t="n">
-        <v>0.8891585330770474</v>
+        <v>0.8869921607200546</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>7</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8213514339012158</v>
+        <v>0.8215426848220275</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>6</v>
       </c>
       <c r="E173" t="n">
-        <v>0.8332427896634498</v>
+        <v>0.8340731221016008</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>6</v>
       </c>
       <c r="E174" t="n">
-        <v>0.8249565085979425</v>
+        <v>0.8237465222676597</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>6</v>
       </c>
       <c r="E175" t="n">
-        <v>0.8414319645274769</v>
+        <v>0.8392549644817006</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>7</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8312315548653211</v>
+        <v>0.8313593427512209</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>7</v>
       </c>
       <c r="E177" t="n">
-        <v>0.8202735135737609</v>
+        <v>0.8221880801312336</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>6</v>
       </c>
       <c r="E178" t="n">
-        <v>0.8362182896546644</v>
+        <v>0.83974926640289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>6</v>
       </c>
       <c r="E179" t="n">
-        <v>0.8456104692786632</v>
+        <v>0.8468090885817404</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>6</v>
       </c>
       <c r="E180" t="n">
-        <v>0.8256316859312732</v>
+        <v>0.8266163943993925</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="E181" t="n">
-        <v>0.8062728779312509</v>
+        <v>0.8075742219261621</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>7</v>
       </c>
       <c r="E182" t="n">
-        <v>0.8528205601855963</v>
+        <v>0.8536671026788578</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>6</v>
       </c>
       <c r="E183" t="n">
-        <v>0.7952636636868873</v>
+        <v>0.7984836221945407</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>6</v>
       </c>
       <c r="E184" t="n">
-        <v>0.7717419874788536</v>
+        <v>0.7719539753114335</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>6</v>
       </c>
       <c r="E185" t="n">
-        <v>0.8352388468655673</v>
+        <v>0.8366726889754786</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>7</v>
       </c>
       <c r="E186" t="n">
-        <v>0.8526741952607126</v>
+        <v>0.8526088348542802</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>0.8568629110702362</v>
+        <v>0.8562650343384407</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>6</v>
       </c>
       <c r="E188" t="n">
-        <v>0.8197468386756049</v>
+        <v>0.821399262457183</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>6</v>
       </c>
       <c r="E189" t="n">
-        <v>0.7701931577740294</v>
+        <v>0.768913259409895</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>5</v>
       </c>
       <c r="E190" t="n">
-        <v>0.7957857883337772</v>
+        <v>0.7953420624588475</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>7</v>
       </c>
       <c r="E191" t="n">
-        <v>0.857432514730126</v>
+        <v>0.8559587748363765</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>7</v>
       </c>
       <c r="E192" t="n">
-        <v>0.8656731518832121</v>
+        <v>0.8646915175698022</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>6</v>
       </c>
       <c r="E193" t="n">
-        <v>0.8217803155532991</v>
+        <v>0.8224143379866475</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>6</v>
       </c>
       <c r="E194" t="n">
-        <v>0.7731888270137287</v>
+        <v>0.7712589971946948</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>5</v>
       </c>
       <c r="E195" t="n">
-        <v>0.7994896498593417</v>
+        <v>0.7976705161007968</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>7</v>
       </c>
       <c r="E196" t="n">
-        <v>0.8776624660299284</v>
+        <v>0.8760577500468554</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>7</v>
       </c>
       <c r="E197" t="n">
-        <v>0.8217639083642121</v>
+        <v>0.8207404905927475</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>6</v>
       </c>
       <c r="E198" t="n">
-        <v>0.8409657767324737</v>
+        <v>0.8417631809157555</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>6</v>
       </c>
       <c r="E199" t="n">
-        <v>0.8308527445552326</v>
+        <v>0.8290187276975074</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>6</v>
       </c>
       <c r="E200" t="n">
-        <v>0.8428569345763235</v>
+        <v>0.8412241141001383</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>7</v>
       </c>
       <c r="E201" t="n">
-        <v>0.8239308442560282</v>
+        <v>0.8219792127265215</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>7</v>
       </c>
       <c r="E202" t="n">
-        <v>0.8669810480885692</v>
+        <v>0.863833816192539</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>6</v>
       </c>
       <c r="E203" t="n">
-        <v>0.8088608727310644</v>
+        <v>0.8075791874317209</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>6</v>
       </c>
       <c r="E204" t="n">
-        <v>0.8195168201369469</v>
+        <v>0.8155948585934111</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>6</v>
       </c>
       <c r="E205" t="n">
-        <v>0.8793427221702808</v>
+        <v>0.8762017163363369</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D206" t="n">
         <v>7</v>
       </c>
       <c r="E206" t="n">
-        <v>0.8691111732526948</v>
+        <v>0.8978808624575838</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>7</v>
       </c>
       <c r="E207" t="n">
-        <v>0.8299554959692137</v>
+        <v>0.8284656344382106</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>6</v>
       </c>
       <c r="E208" t="n">
-        <v>0.8440323574374421</v>
+        <v>0.8427465467741996</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>6</v>
       </c>
       <c r="E209" t="n">
-        <v>0.8349191299592607</v>
+        <v>0.8318077193366158</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -5472,11 +5472,11 @@
         <v>6</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8540438016255697</v>
+        <v>0.8495589819821444</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
         <v>7</v>
       </c>
       <c r="E211" t="n">
-        <v>0.8386364574900267</v>
+        <v>0.8369910975039264</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>7</v>
       </c>
       <c r="E212" t="n">
-        <v>0.8254972956053279</v>
+        <v>0.8257497234261915</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>6</v>
       </c>
       <c r="E213" t="n">
-        <v>0.8438724026535498</v>
+        <v>0.8454578139565209</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>6</v>
       </c>
       <c r="E214" t="n">
-        <v>0.8523232768280339</v>
+        <v>0.8516450843425714</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="E215" t="n">
-        <v>0.8339365251136549</v>
+        <v>0.8328520481032555</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>7</v>
       </c>
       <c r="E216" t="n">
-        <v>0.8114766541325513</v>
+        <v>0.8110699251100615</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>7</v>
       </c>
       <c r="E217" t="n">
-        <v>0.856184441633899</v>
+        <v>0.8552086112475156</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>6</v>
       </c>
       <c r="E218" t="n">
-        <v>0.8001995158917977</v>
+        <v>0.8014548956745803</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>6</v>
       </c>
       <c r="E219" t="n">
-        <v>0.775310511540885</v>
+        <v>0.7737161896445536</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="E220" t="n">
-        <v>0.8410127596421675</v>
+        <v>0.8402490110108346</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>7</v>
       </c>
       <c r="E221" t="n">
-        <v>0.8550382960926404</v>
+        <v>0.8530976073910492</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>7</v>
       </c>
       <c r="E222" t="n">
-        <v>0.8571055441191704</v>
+        <v>0.8547564467998467</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>6</v>
       </c>
       <c r="E223" t="n">
-        <v>0.8218046968633479</v>
+        <v>0.8214334165207063</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>6</v>
       </c>
       <c r="E224" t="n">
-        <v>0.7707372819534457</v>
+        <v>0.7677080655338789</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>5</v>
       </c>
       <c r="E225" t="n">
-        <v>0.7984553756135883</v>
+        <v>0.7958981196085612</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>7</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8586438352411445</v>
+        <v>0.8553515540228951</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>7</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8632896885727392</v>
+        <v>0.8606094663793391</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>6</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8203292639568599</v>
+        <v>0.8189652255087188</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>6</v>
       </c>
       <c r="E229" t="n">
-        <v>0.7715068200621943</v>
+        <v>0.767875560606369</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>5</v>
       </c>
       <c r="E230" t="n">
-        <v>0.7988210085666541</v>
+        <v>0.7949348074017148</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>7</v>
       </c>
       <c r="E231" t="n">
-        <v>0.8745763229601312</v>
+        <v>0.8713255699234781</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="E232" t="n">
-        <v>0.8170422847136791</v>
+        <v>0.8158134966873676</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>6</v>
       </c>
       <c r="E233" t="n">
-        <v>0.835050657542065</v>
+        <v>0.8350027546738134</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>6</v>
       </c>
       <c r="E234" t="n">
-        <v>0.8250660848135901</v>
+        <v>0.8227212260467839</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>6</v>
       </c>
       <c r="E235" t="n">
-        <v>0.8380312269384211</v>
+        <v>0.8349962017752908</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>7</v>
       </c>
       <c r="E236" t="n">
-        <v>0.8184805800560406</v>
+        <v>0.8165394399761294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="E237" t="n">
-        <v>0.8594509361454248</v>
+        <v>0.8575958985442896</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>6</v>
       </c>
       <c r="E238" t="n">
-        <v>0.8383828750764482</v>
+        <v>0.8380461822856556</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>6</v>
       </c>
       <c r="E239" t="n">
-        <v>0.8126325559134436</v>
+        <v>0.8097819968907521</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>6</v>
       </c>
       <c r="E240" t="n">
-        <v>0.8711256330663507</v>
+        <v>0.8684752637689764</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>7</v>
       </c>
       <c r="E241" t="n">
-        <v>0.892636477345168</v>
+        <v>0.8901080459055275</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>7</v>
       </c>
       <c r="E242" t="n">
-        <v>0.8211241484032394</v>
+        <v>0.8222021237768309</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="E243" t="n">
-        <v>0.8340463614222979</v>
+        <v>0.8353861269324717</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>6</v>
       </c>
       <c r="E244" t="n">
-        <v>0.8256504270765518</v>
+        <v>0.8251571173619744</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>6</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8438766436143355</v>
+        <v>0.8417544798417524</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>7</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8297563528085685</v>
+        <v>0.8310617323733684</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>7</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8147502908802997</v>
+        <v>0.818965452229994</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>6</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8323785006397904</v>
+        <v>0.8381035737317019</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>6</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8405715287333788</v>
+        <v>0.844094560603903</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>6</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8414528165200744</v>
+        <v>0.8253967304422398</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -6456,11 +6456,11 @@
         <v>7</v>
       </c>
       <c r="E251" t="n">
-        <v>0.8703155001520595</v>
+        <v>0.8416685569509972</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🔴 Forte activité</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
         <v>7</v>
       </c>
       <c r="E252" t="n">
-        <v>0.8416484341476904</v>
+        <v>0.8467072669905846</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>6</v>
       </c>
       <c r="E253" t="n">
-        <v>0.8229401039354729</v>
+        <v>0.792832480536567</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>6</v>
       </c>
       <c r="E254" t="n">
-        <v>0.7984888264627168</v>
+        <v>0.8029079918909555</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>6</v>
       </c>
       <c r="E255" t="n">
-        <v>0.8257920525290749</v>
+        <v>0.8311791347734856</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -6573,14 +6573,14 @@
         <v>6</v>
       </c>
       <c r="D256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8406156289457072</v>
+        <v>0.8452715247568459</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
         <v>7</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8410147946290296</v>
+        <v>0.8462779088453815</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -6618,17 +6618,17 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D258" t="n">
         <v>6</v>
       </c>
       <c r="E258" t="n">
-        <v>0.8414299993804008</v>
+        <v>0.8115325696540602</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
         <v>6</v>
       </c>
       <c r="E259" t="n">
-        <v>0.8300205577503552</v>
+        <v>0.7969143077580616</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>5</v>
       </c>
       <c r="E260" t="n">
-        <v>0.7807863481117017</v>
+        <v>0.7862388654188677</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -6693,14 +6693,14 @@
         <v>6</v>
       </c>
       <c r="D261" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E261" t="n">
-        <v>0.8410885382180263</v>
+        <v>0.8460244072808161</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -6720,11 +6720,11 @@
         <v>7</v>
       </c>
       <c r="E262" t="n">
-        <v>0.8477271205247052</v>
+        <v>0.8532090138907386</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
         <v>6</v>
       </c>
       <c r="E263" t="n">
-        <v>0.83785951498783</v>
+        <v>0.8465342088179155</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>6</v>
       </c>
       <c r="E264" t="n">
-        <v>0.8301217700495864</v>
+        <v>0.7974503064396405</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>5</v>
       </c>
       <c r="E265" t="n">
-        <v>0.7788130442301432</v>
+        <v>0.7848186131679651</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="E266" t="n">
-        <v>0.858878174213448</v>
+        <v>0.8638434939914281</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
-        <v>0.8396918949110684</v>
+        <v>0.8106761990171492</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>6</v>
       </c>
       <c r="E268" t="n">
-        <v>0.8210389421443747</v>
+        <v>0.8281082191852609</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>6</v>
       </c>
       <c r="E269" t="n">
-        <v>0.8136876062913375</v>
+        <v>0.8173286071931474</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>6</v>
       </c>
       <c r="E270" t="n">
-        <v>0.8210278785589969</v>
+        <v>0.8265365181547223</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>7</v>
       </c>
       <c r="E271" t="n">
-        <v>0.8084224072025625</v>
+        <v>0.8111621394301907</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>7</v>
       </c>
       <c r="E272" t="n">
-        <v>0.8539086743694708</v>
+        <v>0.8546660369608827</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>6</v>
       </c>
       <c r="E273" t="n">
-        <v>0.8306451301382046</v>
+        <v>0.8343453672197131</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>6</v>
       </c>
       <c r="E274" t="n">
-        <v>0.805341751888545</v>
+        <v>0.8056748515427716</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>6</v>
       </c>
       <c r="E275" t="n">
-        <v>0.860651767615116</v>
+        <v>0.8632238127968528</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>7</v>
       </c>
       <c r="E276" t="n">
-        <v>0.8878025430621523</v>
+        <v>0.8876555182717064</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>7</v>
       </c>
       <c r="E277" t="n">
-        <v>0.8202974035970405</v>
+        <v>0.8213393650357687</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>6</v>
       </c>
       <c r="E278" t="n">
-        <v>0.8318130873670482</v>
+        <v>0.8341191513369782</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>6</v>
       </c>
       <c r="E279" t="n">
-        <v>0.8238317508890172</v>
+        <v>0.823776505210183</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>6</v>
       </c>
       <c r="E280" t="n">
-        <v>0.8397483681187485</v>
+        <v>0.8395209167942856</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>7</v>
       </c>
       <c r="E281" t="n">
-        <v>0.8299248817163114</v>
+        <v>0.8307482446254935</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>7</v>
       </c>
       <c r="E282" t="n">
-        <v>0.8186758717073164</v>
+        <v>0.8204039694770935</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>6</v>
       </c>
       <c r="E283" t="n">
-        <v>0.8357137357345736</v>
+        <v>0.8394444639032538</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>6</v>
       </c>
       <c r="E284" t="n">
-        <v>0.8444404120397088</v>
+        <v>0.8456288684498181</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>6</v>
       </c>
       <c r="E285" t="n">
-        <v>0.8245518195508706</v>
+        <v>0.8260574918804747</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>7</v>
       </c>
       <c r="E286" t="n">
-        <v>0.8060473951942477</v>
+        <v>0.8069967053841376</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>7</v>
       </c>
       <c r="E287" t="n">
-        <v>0.8523902507743452</v>
+        <v>0.8518774461264563</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>6</v>
       </c>
       <c r="E288" t="n">
-        <v>0.7944299909803603</v>
+        <v>0.7965960598955252</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>6</v>
       </c>
       <c r="E289" t="n">
-        <v>0.7707246265026055</v>
+        <v>0.7697842217455008</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>6</v>
       </c>
       <c r="E290" t="n">
-        <v>0.8344923438447894</v>
+        <v>0.8351170872197007</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -7416,11 +7416,11 @@
         <v>7</v>
       </c>
       <c r="E291" t="n">
-        <v>0.851524136283181</v>
+        <v>0.8498128447869813</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
         <v>7</v>
       </c>
       <c r="E292" t="n">
-        <v>0.8568261608932959</v>
+        <v>0.8537084165245596</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>6</v>
       </c>
       <c r="E293" t="n">
-        <v>0.8196155543279167</v>
+        <v>0.818821314609412</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>6</v>
       </c>
       <c r="E294" t="n">
-        <v>0.7698664159485789</v>
+        <v>0.7662631526137844</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>5</v>
       </c>
       <c r="E295" t="n">
-        <v>0.7953389485677084</v>
+        <v>0.7926840782165527</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>7</v>
       </c>
       <c r="E296" t="n">
-        <v>0.8577934178439055</v>
+        <v>0.8535023506241617</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>7</v>
       </c>
       <c r="E297" t="n">
-        <v>0.8627079592810738</v>
+        <v>0.8597861155114994</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>6</v>
       </c>
       <c r="E298" t="n">
-        <v>0.8198364575703939</v>
+        <v>0.8178493928427648</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>6</v>
       </c>
       <c r="E299" t="n">
-        <v>0.7709817452864214</v>
+        <v>0.7669325428779681</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>5</v>
       </c>
       <c r="E300" t="n">
-        <v>0.7985405054959384</v>
+        <v>0.7937078186959932</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>7</v>
       </c>
       <c r="E301" t="n">
-        <v>0.8736253699871026</v>
+        <v>0.8701379275081135</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>7</v>
       </c>
       <c r="E302" t="n">
-        <v>0.8172428625142593</v>
+        <v>0.8152862785526513</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>6</v>
       </c>
       <c r="E303" t="n">
-        <v>0.8358291905335706</v>
+        <v>0.8351747339422053</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>6</v>
       </c>
       <c r="E304" t="n">
-        <v>0.8258918078258786</v>
+        <v>0.8228666613800358</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>6</v>
       </c>
       <c r="E305" t="n">
-        <v>0.8377716613538337</v>
+        <v>0.8342579133582837</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>7</v>
       </c>
       <c r="E306" t="n">
-        <v>0.819453030265599</v>
+        <v>0.8166861104070711</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>7</v>
       </c>
       <c r="E307" t="n">
-        <v>0.8614216635237526</v>
+        <v>0.8580935947478765</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>6</v>
       </c>
       <c r="E308" t="n">
-        <v>0.8407581574989088</v>
+        <v>0.8390173550808069</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>6</v>
       </c>
       <c r="E309" t="n">
-        <v>0.8137891629729609</v>
+        <v>0.8095567997055826</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>6</v>
       </c>
       <c r="E310" t="n">
-        <v>0.8730099562442664</v>
+        <v>0.8690561814741655</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>0.8953918351067438</v>
+        <v>0.8911597849142673</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>7</v>
       </c>
       <c r="E312" t="n">
-        <v>0.8241418326571908</v>
+        <v>0.8232963652837845</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="E313" t="n">
-        <v>0.8373614080024488</v>
+        <v>0.8365251584486528</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>6</v>
       </c>
       <c r="E314" t="n">
-        <v>0.8286111764233522</v>
+        <v>0.8260467799022946</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>6</v>
       </c>
       <c r="E315" t="n">
-        <v>0.8471666682850231</v>
+        <v>0.8429103042140151</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>7</v>
       </c>
       <c r="E316" t="n">
-        <v>0.8328668104449737</v>
+        <v>0.8320297685708491</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="E317" t="n">
-        <v>0.8191907388651355</v>
+        <v>0.8208849935820609</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>6</v>
       </c>
       <c r="E318" t="n">
-        <v>0.8366289427786163</v>
+        <v>0.8395890418929284</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>6</v>
       </c>
       <c r="E319" t="n">
-        <v>0.8450162290322661</v>
+        <v>0.8457992293617943</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>6</v>
       </c>
       <c r="E320" t="n">
-        <v>0.8267515139146285</v>
+        <v>0.8268535883739742</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>7</v>
       </c>
       <c r="E321" t="n">
-        <v>0.8045517727410123</v>
+        <v>0.8057822293533392</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -8160,11 +8160,11 @@
         <v>7</v>
       </c>
       <c r="E322" t="n">
-        <v>0.8485898947474934</v>
+        <v>0.85010193815135</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
         <v>6</v>
       </c>
       <c r="E323" t="n">
-        <v>0.8296141576285314</v>
+        <v>0.7955941070209851</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>6</v>
       </c>
       <c r="E324" t="n">
-        <v>0.8057807358828459</v>
+        <v>0.7688311133721863</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>6</v>
       </c>
       <c r="E325" t="n">
-        <v>0.8324960145083341</v>
+        <v>0.8340955503059155</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>7</v>
       </c>
       <c r="E326" t="n">
-        <v>0.8473610926156093</v>
+        <v>0.848180920186669</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -8280,11 +8280,11 @@
         <v>7</v>
       </c>
       <c r="E327" t="n">
-        <v>0.8491886625386249</v>
+        <v>0.8500095328899346</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="E328" t="n">
-        <v>0.8128732430814493</v>
+        <v>0.8160087267557781</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>6</v>
       </c>
       <c r="E329" t="n">
-        <v>0.8007173225133106</v>
+        <v>0.8008535992015493</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>5</v>
       </c>
       <c r="E330" t="n">
-        <v>0.7890753746032715</v>
+        <v>0.7899170499859434</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>7</v>
       </c>
       <c r="E331" t="n">
-        <v>0.8492361752673834</v>
+        <v>0.8492964879430906</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>7</v>
       </c>
       <c r="E332" t="n">
-        <v>0.8551586517179857</v>
+        <v>0.8558850697796756</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>6</v>
       </c>
       <c r="E333" t="n">
-        <v>0.8108398167773931</v>
+        <v>0.8133131181350862</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>6</v>
       </c>
       <c r="E334" t="n">
-        <v>0.8007123060900756</v>
+        <v>0.8004769460119383</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>5</v>
       </c>
       <c r="E335" t="n">
-        <v>0.7893006368116899</v>
+        <v>0.7893394701408617</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>7</v>
       </c>
       <c r="E336" t="n">
-        <v>0.8663720699271772</v>
+        <v>0.8666184887741553</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>7</v>
       </c>
       <c r="E337" t="n">
-        <v>0.8439151308409236</v>
+        <v>0.8118265531795883</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>6</v>
       </c>
       <c r="E338" t="n">
-        <v>0.8277238113711579</v>
+        <v>0.8306002713213064</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>6</v>
       </c>
       <c r="E339" t="n">
-        <v>0.8183611041367658</v>
+        <v>0.8184422868670841</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>6</v>
       </c>
       <c r="E340" t="n">
-        <v>0.8289302695881237</v>
+        <v>0.8294837474822998</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>7</v>
       </c>
       <c r="E341" t="n">
-        <v>0.8128073721221</v>
+        <v>0.8127027122145264</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>0.855845744475658</v>
+        <v>0.8548087027853875</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>6</v>
       </c>
       <c r="E343" t="n">
-        <v>0.8335201812512947</v>
+        <v>0.8345897823873193</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>6</v>
       </c>
       <c r="E344" t="n">
-        <v>0.8081553680728182</v>
+        <v>0.8063748990646518</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="E345" t="n">
-        <v>0.8648950909123276</v>
+        <v>0.8642206770001035</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>7</v>
       </c>
       <c r="E346" t="n">
-        <v>0.8895241612135762</v>
+        <v>0.8876517372901994</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>7</v>
       </c>
       <c r="E347" t="n">
-        <v>0.819423074846144</v>
+        <v>0.8200564425745053</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>6</v>
       </c>
       <c r="E348" t="n">
-        <v>0.8309958390515261</v>
+        <v>0.8322960463437168</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>6</v>
       </c>
       <c r="E349" t="n">
-        <v>0.8232785234547626</v>
+        <v>0.8225297205375903</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>6</v>
       </c>
       <c r="E350" t="n">
-        <v>0.8399250940843062</v>
+        <v>0.8381475318561901</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="E351" t="n">
-        <v>0.8272361669361505</v>
+        <v>0.8278665690539032</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>7</v>
       </c>
       <c r="E352" t="n">
-        <v>0.8148344942673633</v>
+        <v>0.8174354620654174</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>6</v>
       </c>
       <c r="E353" t="n">
-        <v>0.8315304818779532</v>
+        <v>0.8358137631657149</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>6</v>
       </c>
       <c r="E354" t="n">
-        <v>0.8400252611950192</v>
+        <v>0.8419416167519311</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>6</v>
       </c>
       <c r="E355" t="n">
-        <v>0.8396730940751356</v>
+        <v>0.8413850502534347</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>7</v>
       </c>
       <c r="E356" t="n">
-        <v>0.8380060732622684</v>
+        <v>0.8402012815379134</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>7</v>
       </c>
       <c r="E357" t="n">
-        <v>0.8438584057971686</v>
+        <v>0.8457399137092361</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>6</v>
       </c>
       <c r="E358" t="n">
-        <v>0.8246234691504276</v>
+        <v>0.8291502673216541</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>6</v>
       </c>
       <c r="E359" t="n">
-        <v>0.8002870805335769</v>
+        <v>0.8015963067912093</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>6</v>
       </c>
       <c r="E360" t="n">
-        <v>0.8269353490887266</v>
+        <v>0.8294581066478383</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -9093,14 +9093,14 @@
         <v>6</v>
       </c>
       <c r="D361" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E361" t="n">
-        <v>0.8429199469209923</v>
+        <v>0.843997627797753</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
         <v>7</v>
       </c>
       <c r="E362" t="n">
-        <v>0.8451903227603799</v>
+        <v>0.8459103950346361</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>6</v>
       </c>
       <c r="E363" t="n">
-        <v>0.8082548584600893</v>
+        <v>0.8113124611401799</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>6</v>
       </c>
       <c r="E364" t="n">
-        <v>0.7964141489279392</v>
+        <v>0.7964581576260654</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>5</v>
       </c>
       <c r="E365" t="n">
-        <v>0.7840383052825928</v>
+        <v>0.7850062196904962</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>7</v>
       </c>
       <c r="E366" t="n">
-        <v>0.8463434980373191</v>
+        <v>0.846316862587977</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>7</v>
       </c>
       <c r="E367" t="n">
-        <v>0.8519213006954002</v>
+        <v>0.852568354269471</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>6</v>
       </c>
       <c r="E368" t="n">
-        <v>0.8438983397050337</v>
+        <v>0.8462182825261897</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>6</v>
       </c>
       <c r="E369" t="n">
-        <v>0.7972351661836259</v>
+        <v>0.7969040413095494</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>5</v>
       </c>
       <c r="E370" t="n">
-        <v>0.7848256573532567</v>
+        <v>0.7847433379202178</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>7</v>
       </c>
       <c r="E371" t="n">
-        <v>0.8619712819956771</v>
+        <v>0.8620829293222139</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>7</v>
       </c>
       <c r="E372" t="n">
-        <v>0.8407063091988173</v>
+        <v>0.8414171612451948</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>6</v>
       </c>
       <c r="E373" t="n">
-        <v>0.8234310439138701</v>
+        <v>0.8262105012180829</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>6</v>
       </c>
       <c r="E374" t="n">
-        <v>0.8152445879849523</v>
+        <v>0.8152187833882343</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>6</v>
       </c>
       <c r="E375" t="n">
-        <v>0.8242704290332217</v>
+        <v>0.8246914328950824</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>7</v>
       </c>
       <c r="E376" t="n">
-        <v>0.8092636635465196</v>
+        <v>0.8090639682043167</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>7</v>
       </c>
       <c r="E377" t="n">
-        <v>0.8847908058551828</v>
+        <v>0.8835907897563897</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>6</v>
       </c>
       <c r="E378" t="n">
-        <v>0.8288211461269495</v>
+        <v>0.8298079389514346</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>6</v>
       </c>
       <c r="E379" t="n">
-        <v>0.8034765238713737</v>
+        <v>0.801579879991936</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>6</v>
       </c>
       <c r="E380" t="n">
-        <v>0.8603032357764967</v>
+        <v>0.8594837405464866</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>7</v>
       </c>
       <c r="E381" t="n">
-        <v>0.8848112183387835</v>
+        <v>0.8828308076569529</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>7</v>
       </c>
       <c r="E382" t="n">
-        <v>0.8155158931902822</v>
+        <v>0.8160686905765947</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>6</v>
       </c>
       <c r="E383" t="n">
-        <v>0.8271739001225944</v>
+        <v>0.8283695163148823</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>6</v>
       </c>
       <c r="E384" t="n">
-        <v>0.8194302308439005</v>
+        <v>0.8185797508316812</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>6</v>
       </c>
       <c r="E385" t="n">
-        <v>0.8352950775262081</v>
+        <v>0.8334054730155251</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>7</v>
       </c>
       <c r="E386" t="n">
-        <v>0.8247272362784734</v>
+        <v>0.825279722310076</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>7</v>
       </c>
       <c r="E387" t="n">
-        <v>0.8111802840129638</v>
+        <v>0.8136855644237084</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>6</v>
       </c>
       <c r="E388" t="n">
-        <v>0.8276463783148564</v>
+        <v>0.8318032495903247</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>6</v>
       </c>
       <c r="E389" t="n">
-        <v>0.8363637538871381</v>
+        <v>0.8381813704365433</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>6</v>
       </c>
       <c r="E390" t="n">
-        <v>0.8357947884183942</v>
+        <v>0.8373952357455938</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>7</v>
       </c>
       <c r="E391" t="n">
-        <v>0.867149491330762</v>
+        <v>0.8692838130747258</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>7</v>
       </c>
       <c r="E392" t="n">
-        <v>0.8401549825764667</v>
+        <v>0.8419442297232274</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>6</v>
       </c>
       <c r="E393" t="n">
-        <v>0.8199100205392549</v>
+        <v>0.8243026853811861</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>6</v>
       </c>
       <c r="E394" t="n">
-        <v>0.7964498177923338</v>
+        <v>0.7976561580041444</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>6</v>
       </c>
       <c r="E395" t="n">
-        <v>0.8224634618470164</v>
+        <v>0.8248498728781035</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="E396" t="n">
-        <v>0.8389609124925402</v>
+        <v>0.8399296866522896</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>7</v>
       </c>
       <c r="E397" t="n">
-        <v>0.84149166791126</v>
+        <v>0.8421430563685871</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>6</v>
       </c>
       <c r="E398" t="n">
-        <v>0.8406959302497632</v>
+        <v>0.8436204881379099</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>6</v>
       </c>
       <c r="E399" t="n">
-        <v>0.8299677444226815</v>
+        <v>0.8299239404273756</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>5</v>
       </c>
       <c r="E400" t="n">
-        <v>0.779527895378344</v>
+        <v>0.7803659439086914</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>6</v>
       </c>
       <c r="E401" t="n">
-        <v>0.84180493306632</v>
+        <v>0.8416515022817285</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="E402" t="n">
-        <v>0.8480823280835393</v>
+        <v>0.848608414332072</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>6</v>
       </c>
       <c r="E403" t="n">
-        <v>0.8395580233949603</v>
+        <v>0.8417750271883877</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>6</v>
       </c>
       <c r="E404" t="n">
-        <v>0.8313808850567751</v>
+        <v>0.7932074840622719</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>5</v>
       </c>
       <c r="E405" t="n">
-        <v>0.780101458231608</v>
+        <v>0.7798905878356008</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>7</v>
       </c>
       <c r="E406" t="n">
-        <v>0.8584327842250016</v>
+        <v>0.8584647274980642</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -10200,11 +10200,11 @@
         <v>7</v>
       </c>
       <c r="E407" t="n">
-        <v>0.8370201377813608</v>
+        <v>0.8704720327864479</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>🔴 Forte activité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
         <v>6</v>
       </c>
       <c r="E408" t="n">
-        <v>0.8198536068502099</v>
+        <v>0.822520354781488</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>6</v>
       </c>
       <c r="E409" t="n">
-        <v>0.811186908471464</v>
+        <v>0.8110634245053687</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>6</v>
       </c>
       <c r="E410" t="n">
-        <v>0.8200461069742838</v>
+        <v>0.8203346946022727</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>7</v>
       </c>
       <c r="E411" t="n">
-        <v>0.8383970498006582</v>
+        <v>0.8380611169905891</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>7</v>
       </c>
       <c r="E412" t="n">
-        <v>0.8805159125665223</v>
+        <v>0.8792163386489407</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="E413" t="n">
-        <v>0.825129605302907</v>
+        <v>0.8259932850346421</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>6</v>
       </c>
       <c r="E414" t="n">
-        <v>0.7996635966830785</v>
+        <v>0.7976769678520435</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>6</v>
       </c>
       <c r="E415" t="n">
-        <v>0.8559116088982784</v>
+        <v>0.8549770225178112</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>7</v>
       </c>
       <c r="E416" t="n">
-        <v>0.8811279306508075</v>
+        <v>0.8790413442284171</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>7</v>
       </c>
       <c r="E417" t="n">
-        <v>0.8449789765593294</v>
+        <v>0.8126110535163384</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>6</v>
       </c>
       <c r="E418" t="n">
-        <v>0.822577127302536</v>
+        <v>0.8236347063623294</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>6</v>
       </c>
       <c r="E419" t="n">
-        <v>0.8149130175812077</v>
+        <v>0.8139531419734763</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>6</v>
       </c>
       <c r="E420" t="n">
-        <v>0.8308612361098781</v>
+        <v>0.828853549379291</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>7</v>
       </c>
       <c r="E421" t="n">
-        <v>0.8212913957681148</v>
+        <v>0.8217286065887408</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -10560,11 +10560,11 @@
         <v>7</v>
       </c>
       <c r="E422" t="n">
-        <v>0.8739498098519286</v>
+        <v>0.8435908953348796</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🔴 Forte activité</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
         <v>6</v>
       </c>
       <c r="E423" t="n">
-        <v>0.8235167325145067</v>
+        <v>0.8275563259317418</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>6</v>
       </c>
       <c r="E424" t="n">
-        <v>0.8329007119843456</v>
+        <v>0.8346281629620178</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>6</v>
       </c>
       <c r="E425" t="n">
-        <v>0.8504822952578767</v>
+        <v>0.8520033046452686</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -10650,13 +10650,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D426" t="n">
         <v>7</v>
       </c>
       <c r="E426" t="n">
-        <v>0.8964950484458847</v>
+        <v>0.8656985811340862</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>7</v>
       </c>
       <c r="E427" t="n">
-        <v>0.8365504669420648</v>
+        <v>0.8382404332209116</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>6</v>
       </c>
       <c r="E428" t="n">
-        <v>0.8158000430675468</v>
+        <v>0.820086900633995</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>6</v>
       </c>
       <c r="E429" t="n">
-        <v>0.8305874208007197</v>
+        <v>0.8317799158770629</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="E430" t="n">
-        <v>0.8178189884532582</v>
+        <v>0.8200720295761571</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>6</v>
       </c>
       <c r="E431" t="n">
-        <v>0.8341873944407763</v>
+        <v>0.835049128291583</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>7</v>
       </c>
       <c r="E432" t="n">
-        <v>0.8378413590517912</v>
+        <v>0.8383681557395243</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>6</v>
       </c>
       <c r="E433" t="n">
-        <v>0.8369446523261792</v>
+        <v>0.8397663867834843</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -10848,11 +10848,11 @@
         <v>6</v>
       </c>
       <c r="E434" t="n">
-        <v>0.8256702471261073</v>
+        <v>0.8632287930960607</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
         <v>5</v>
       </c>
       <c r="E435" t="n">
-        <v>0.7749561974496553</v>
+        <v>0.7756700660243179</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>6</v>
       </c>
       <c r="E436" t="n">
-        <v>0.8375133312109746</v>
+        <v>0.8372676757851033</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>7</v>
       </c>
       <c r="E437" t="n">
-        <v>0.8438343712777804</v>
+        <v>0.8442465343860666</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>6</v>
       </c>
       <c r="E438" t="n">
-        <v>0.8350732398755623</v>
+        <v>0.8371658903179746</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -10968,11 +10968,11 @@
         <v>6</v>
       </c>
       <c r="E439" t="n">
-        <v>0.8259744186594029</v>
+        <v>0.8630796658872354</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
         <v>5</v>
       </c>
       <c r="E440" t="n">
-        <v>0.7757155028256503</v>
+        <v>0.7753796794197776</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>7</v>
       </c>
       <c r="E441" t="n">
-        <v>0.8543207958491162</v>
+        <v>0.8542286362310854</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>7</v>
       </c>
       <c r="E442" t="n">
-        <v>0.8658817251351318</v>
+        <v>0.8663572721495085</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>6</v>
       </c>
       <c r="E443" t="n">
-        <v>0.815679497188992</v>
+        <v>0.8182094434295039</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>6</v>
       </c>
       <c r="E444" t="n">
-        <v>0.8075796594523421</v>
+        <v>0.8073551004583187</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>5</v>
       </c>
       <c r="E445" t="n">
-        <v>0.8152612628358783</v>
+        <v>0.8154376998092189</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>7</v>
       </c>
       <c r="E446" t="n">
-        <v>0.8354836624938173</v>
+        <v>0.8350755504371457</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>7</v>
       </c>
       <c r="E447" t="n">
-        <v>0.8773338915121677</v>
+        <v>0.8759506061823682</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>6</v>
       </c>
       <c r="E448" t="n">
-        <v>0.8207811201461639</v>
+        <v>0.8215208583407932</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>6</v>
       </c>
       <c r="E449" t="n">
-        <v>0.7962272624776823</v>
+        <v>0.7941467834241464</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>6</v>
       </c>
       <c r="E450" t="n">
-        <v>0.8514431317647299</v>
+        <v>0.8503928545749548</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>7</v>
       </c>
       <c r="E451" t="n">
-        <v>0.8765641896411627</v>
+        <v>0.8743586829214386</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>7</v>
       </c>
       <c r="E452" t="n">
-        <v>0.8418595876872627</v>
+        <v>0.8422861195573904</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>6</v>
       </c>
       <c r="E453" t="n">
-        <v>0.8185690725692596</v>
+        <v>0.8195268963322495</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>6</v>
       </c>
       <c r="E454" t="n">
-        <v>0.8116920789082847</v>
+        <v>0.8106316701330321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>6</v>
       </c>
       <c r="E455" t="n">
-        <v>0.8263387896797874</v>
+        <v>0.8241934415065881</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>7</v>
       </c>
       <c r="E456" t="n">
-        <v>0.8170392537357832</v>
+        <v>0.8173860013915004</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>7</v>
       </c>
       <c r="E457" t="n">
-        <v>0.8697765351717951</v>
+        <v>0.872279414194831</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>6</v>
       </c>
       <c r="E458" t="n">
-        <v>0.8193102846241962</v>
+        <v>0.8232544528113472</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>6</v>
       </c>
       <c r="E459" t="n">
-        <v>0.8286059504807599</v>
+        <v>0.8302039329451745</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>6</v>
       </c>
       <c r="E460" t="n">
-        <v>0.8833365946105032</v>
+        <v>0.884754144784176</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>7</v>
       </c>
       <c r="E461" t="n">
-        <v>0.8918962478637696</v>
+        <v>0.8939096277410334</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>5</v>
       </c>
       <c r="E462" t="n">
-        <v>0.7996494408809778</v>
+        <v>0.8027518301299124</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
